--- a/artfynd/A 16733-2025 artfynd.xlsx
+++ b/artfynd/A 16733-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16306329</v>
+        <v>16306314</v>
       </c>
       <c r="B2" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626825.7942939887</v>
+        <v>626795</v>
       </c>
       <c r="R2" t="n">
-        <v>6698938.34088102</v>
+        <v>6698976</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2012-06-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-06-08</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På levande ek, omkr. 370 cm.</t>
+          <t>På levande ek, omkr. 302 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,6 +789,1095 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>16306315</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nöttbo vid Untrafjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>626878</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6698839</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Söderfors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2012-06-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-06-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På levande ek, omkr. 322 cm.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Medelåldrig lövskog med inslag av gamla ekar, (f.d. hage).</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16306329</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nöttbo vid Untrafjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>626826</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6698938</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Söderfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-06-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-06-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På levande ek, omkr. 370 cm.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Medelåldrig lövskog med inslag av gamla ekar, (f.d. hage).</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16356834</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93136</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nöttbo vid Untrafjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>626898</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6698801</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Söderfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-06-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-06-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 dm2 på naken ved på död, kvarsittande gren 2 m upp, på levande ek, omkr. 324 cm.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Medelåldrig lövskog med inslag av gamla ekar, (f.d. hage).</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Naken ved på död, kvarsittande gren, på levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16356840</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93136</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nöttbo vid Untrafjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>626795</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6698976</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Söderfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-06-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-06-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>8 dm2 på naken ved på nedfallen gren, omkr. 98 cm, från levande ek, omkr. 302 cm.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Medelåldrig lövskog med inslag av gamla ekar, (f.d. hage).</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Naken ved på nedfallen gren från levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16446927</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nöttbo vid Untrafjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>626916</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6698762</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Söderfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2012-01-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2012-01-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 ex. på död, kvarsittande gren, på levande ek, omkr. 35 cm. OVANLIGT SUBSTRAT!</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Bryn mot kraftledningsgata.</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Död, kvarsittande gren på levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>16354037</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nöttbo vid Untrafjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>626878</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6698839</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Söderfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-06-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-06-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ex. på levande ek, omkr. 322 cm.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Medelåldrig lövskog med inslag av gamla ekar, (f.d. hage).</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16442833</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nöttbo vid Untrafjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626982</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6698731</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Söderfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-06-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-06-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På levande ek med stort stamsår, omkr. 347 cm.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>50-årig granplantering.</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>16442858</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nöttbo vid Untrafjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626883</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6698841</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Söderfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2012-06-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2012-06-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På levande ek, omkr. 308 cm.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Medelåldrig lövskog med inslag av gamla ekar, (f.d. hage).</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16442860</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nöttbo vid Untrafjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626973</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6698688</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Söderfors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2012-06-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2012-06-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På levande ek, omkr. 318 cm.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>50-årig granplantering.</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16733-2025 artfynd.xlsx
+++ b/artfynd/A 16733-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16306314</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16306315</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16306329</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16356834</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1275,6 +1300,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16356840</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1401,6 +1431,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16446927</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1527,6 +1562,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16354037</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1644,6 +1684,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16442833</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1761,6 +1806,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16442858</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1878,8 +1928,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16442860</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>